--- a/artfynd/A 11648-2024 artfynd.xlsx
+++ b/artfynd/A 11648-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -921,6 +921,108 @@
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>129302342</v>
+      </c>
+      <c r="B4" t="n">
+        <v>98647</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>219798</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Epipactis helleborine</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Hofterup, väster E6, Sk</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>372420</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6184084</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Kävlinge</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Hofterup</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>Läplantering i åkermark</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Charlotte Wigermo</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Charlotte Wigermo, Åke Svensson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 11648-2024 artfynd.xlsx
+++ b/artfynd/A 11648-2024 artfynd.xlsx
@@ -926,7 +926,7 @@
         <v>129302342</v>
       </c>
       <c r="B4" t="n">
-        <v>98647</v>
+        <v>98654</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 11648-2024 artfynd.xlsx
+++ b/artfynd/A 11648-2024 artfynd.xlsx
@@ -926,7 +926,7 @@
         <v>129302342</v>
       </c>
       <c r="B4" t="n">
-        <v>98654</v>
+        <v>98656</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 11648-2024 artfynd.xlsx
+++ b/artfynd/A 11648-2024 artfynd.xlsx
@@ -926,7 +926,7 @@
         <v>129302342</v>
       </c>
       <c r="B4" t="n">
-        <v>98656</v>
+        <v>98682</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 11648-2024 artfynd.xlsx
+++ b/artfynd/A 11648-2024 artfynd.xlsx
@@ -926,7 +926,7 @@
         <v>129302342</v>
       </c>
       <c r="B4" t="n">
-        <v>98682</v>
+        <v>98683</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 11648-2024 artfynd.xlsx
+++ b/artfynd/A 11648-2024 artfynd.xlsx
@@ -926,7 +926,7 @@
         <v>129302342</v>
       </c>
       <c r="B4" t="n">
-        <v>98683</v>
+        <v>98684</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 11648-2024 artfynd.xlsx
+++ b/artfynd/A 11648-2024 artfynd.xlsx
@@ -926,7 +926,7 @@
         <v>129302342</v>
       </c>
       <c r="B4" t="n">
-        <v>98684</v>
+        <v>98688</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 11648-2024 artfynd.xlsx
+++ b/artfynd/A 11648-2024 artfynd.xlsx
@@ -926,7 +926,7 @@
         <v>129302342</v>
       </c>
       <c r="B4" t="n">
-        <v>98734</v>
+        <v>98746</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 11648-2024 artfynd.xlsx
+++ b/artfynd/A 11648-2024 artfynd.xlsx
@@ -926,7 +926,7 @@
         <v>129302342</v>
       </c>
       <c r="B4" t="n">
-        <v>98746</v>
+        <v>98747</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 11648-2024 artfynd.xlsx
+++ b/artfynd/A 11648-2024 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>77926304</v>
       </c>
       <c r="B2" t="n">
-        <v>9299</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>9403</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -728,10 +723,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>372346.7912593578</v>
+        <v>372347</v>
       </c>
       <c r="R2" t="n">
-        <v>6184153.908223684</v>
+        <v>6184154</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -761,19 +756,9 @@
           <t>2019-05-21</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2019-05-21</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -806,57 +791,48 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>96377211</v>
+        <v>129302342</v>
       </c>
       <c r="B3" t="n">
-        <v>103813</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99096</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220785</v>
+        <v>219798</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Hofterup V E6, Sk</t>
+          <t>Hofterup, väster E6, Sk</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>372355.7697232804</v>
+        <v>372420</v>
       </c>
       <c r="R3" t="n">
-        <v>6184152.519309599</v>
+        <v>6184084</v>
       </c>
       <c r="S3" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -880,22 +856,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2021-09-18</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>10:20</t>
+          <t>2025-10-19</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2021-09-18</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>11:30</t>
+          <t>2025-10-19</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -904,67 +870,75 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>Läplantering i åkermark</t>
+        </is>
+      </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Owe Rosengren</t>
+          <t>Charlotte Wigermo</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Owe Rosengren, Joakim Ekman, Håkan Andersson</t>
+          <t>Charlotte Wigermo, Åke Svensson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129302342</v>
+        <v>96377211</v>
       </c>
       <c r="B4" t="n">
-        <v>98997</v>
+        <v>106813</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>219798</v>
+        <v>220785</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Hofterup, väster E6, Sk</t>
+          <t>Hofterup V E6, Sk</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>372420</v>
+        <v>372356</v>
       </c>
       <c r="R4" t="n">
-        <v>6184084</v>
+        <v>6184153</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -988,12 +962,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-10-19</t>
+          <t>2021-09-18</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-10-19</t>
+          <t>2021-09-18</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1002,23 +986,19 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>Läplantering i åkermark</t>
-        </is>
-      </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Charlotte Wigermo</t>
+          <t>Owe Rosengren</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Charlotte Wigermo, Åke Svensson</t>
+          <t>Owe Rosengren, Joakim Ekman, Håkan Andersson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>

--- a/artfynd/A 11648-2024 artfynd.xlsx
+++ b/artfynd/A 11648-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -788,6 +793,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/77926304</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -900,6 +910,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96377211</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1002,8 +1017,18 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129302342</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>